--- a/Basic Practise File.xlsx
+++ b/Basic Practise File.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D601EDF-BFDC-43C1-A4E9-A7E0EA652CED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B134B972-3163-4958-B1B1-E9A2C8E77AD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="955" activeTab="4" xr2:uid="{804A284F-30AB-4AA4-80D9-3863464D9C5B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="955" activeTab="5" xr2:uid="{804A284F-30AB-4AA4-80D9-3863464D9C5B}"/>
   </bookViews>
   <sheets>
     <sheet name="Introduction" sheetId="13" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="319">
   <si>
     <t>Employee Name</t>
   </si>
@@ -936,6 +936,75 @@
   </si>
   <si>
     <t>random number will be displaying.</t>
+  </si>
+  <si>
+    <t>b+a</t>
+  </si>
+  <si>
+    <t>c-a</t>
+  </si>
+  <si>
+    <t>d*a</t>
+  </si>
+  <si>
+    <t>e/a</t>
+  </si>
+  <si>
+    <t>ctrl+c(a)</t>
+  </si>
+  <si>
+    <t>*=h2*(fn+f4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">it will become </t>
+  </si>
+  <si>
+    <t>float into integer</t>
+  </si>
+  <si>
+    <t>round to near by value</t>
+  </si>
+  <si>
+    <t>roundup means to nearest higest integer</t>
+  </si>
+  <si>
+    <t>roundup means to nearest lowest integer</t>
+  </si>
+  <si>
+    <t>*=int(a2)</t>
+  </si>
+  <si>
+    <t>*=round(a2,0)</t>
+  </si>
+  <si>
+    <t>*=roundup(a2,0)</t>
+  </si>
+  <si>
+    <t>*=power(g2,h2)</t>
+  </si>
+  <si>
+    <t>*=g2^h2</t>
+  </si>
+  <si>
+    <t>*=roman(k2)</t>
+  </si>
+  <si>
+    <t>*=arabic(n2)</t>
+  </si>
+  <si>
+    <t>*=rept(q2,5)</t>
+  </si>
+  <si>
+    <t>*=rept(([s] fn+f4),q2)</t>
+  </si>
+  <si>
+    <t>*=sqrt(u2)</t>
+  </si>
+  <si>
+    <t>*=abs(x2)</t>
+  </si>
+  <si>
+    <t>5=number of times reption</t>
   </si>
 </sst>
 </file>
@@ -3517,7 +3586,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="str">
-        <f t="shared" ref="F1:F11" si="0">E2</f>
+        <f t="shared" ref="F2:F11" si="0">E2</f>
         <v>JP Kumar</v>
       </c>
     </row>
@@ -3686,6 +3755,9 @@
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:J16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="9" max="9" width="12.7265625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -3729,6 +3801,17 @@
       <c r="E2">
         <v>0.1111111111111111</v>
       </c>
+      <c r="H2">
+        <v>54</v>
+      </c>
+      <c r="I2">
+        <f>H2*$I$1</f>
+        <v>540</v>
+      </c>
+      <c r="J2">
+        <f>H2*-($J$1)</f>
+        <v>54</v>
+      </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3">
@@ -3746,6 +3829,17 @@
       <c r="E3">
         <v>1.875</v>
       </c>
+      <c r="H3">
+        <v>16</v>
+      </c>
+      <c r="I3">
+        <f t="shared" ref="I3:I10" si="0">H3*$I$1</f>
+        <v>160</v>
+      </c>
+      <c r="J3">
+        <f t="shared" ref="J3:J10" si="1">H3*-($J$1)</f>
+        <v>16</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4">
@@ -3763,6 +3857,17 @@
       <c r="E4">
         <v>7.2727272727272724E-2</v>
       </c>
+      <c r="H4">
+        <v>55</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="0"/>
+        <v>550</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="1"/>
+        <v>55</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5">
@@ -3780,6 +3885,17 @@
       <c r="E5">
         <v>7.1428571428571425E-2</v>
       </c>
+      <c r="H5">
+        <v>28</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="0"/>
+        <v>280</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6">
@@ -3797,6 +3913,17 @@
       <c r="E6">
         <v>1.2058823529411764</v>
       </c>
+      <c r="H6">
+        <v>34</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="0"/>
+        <v>340</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7">
@@ -3814,6 +3941,17 @@
       <c r="E7">
         <v>0.50909090909090904</v>
       </c>
+      <c r="H7">
+        <v>55</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="0"/>
+        <v>550</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="1"/>
+        <v>55</v>
+      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8">
@@ -3831,6 +3969,17 @@
       <c r="E8">
         <v>9.5238095238095233E-2</v>
       </c>
+      <c r="H8">
+        <v>63</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="0"/>
+        <v>630</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="1"/>
+        <v>63</v>
+      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9">
@@ -3848,6 +3997,17 @@
       <c r="E9">
         <v>0.6428571428571429</v>
       </c>
+      <c r="H9">
+        <v>28</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="0"/>
+        <v>280</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10">
@@ -3865,6 +4025,31 @@
       <c r="E10">
         <v>0.63461538461538458</v>
       </c>
+      <c r="H10">
+        <v>52</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="0"/>
+        <v>520</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B11" t="s">
+        <v>296</v>
+      </c>
+      <c r="C11" t="s">
+        <v>297</v>
+      </c>
+      <c r="D11" t="s">
+        <v>298</v>
+      </c>
+      <c r="E11" t="s">
+        <v>299</v>
+      </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
@@ -3873,11 +4058,20 @@
       <c r="B12" t="s">
         <v>295</v>
       </c>
+      <c r="H12" t="s">
+        <v>300</v>
+      </c>
+      <c r="I12" t="s">
+        <v>301</v>
+      </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13">
         <f ca="1">RAND()</f>
-        <v>0.99342984199361239</v>
+        <v>0.96855091489393363</v>
+      </c>
+      <c r="I13" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
@@ -3904,12 +4098,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05B184E8-5ED5-4908-B896-9965F809130A}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:Y10"/>
+  <dimension ref="A1:Y18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="5" max="5" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.7265625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="23.453125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.35">
@@ -3978,213 +4178,685 @@
       <c r="A2">
         <v>5.46</v>
       </c>
+      <c r="B2">
+        <f>INT(A2)</f>
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <f>ROUND(A2,0)</f>
+        <v>5</v>
+      </c>
+      <c r="D2">
+        <f>ROUNDUP(A2,0)</f>
+        <v>6</v>
+      </c>
+      <c r="E2">
+        <f>ROUNDDOWN(A2,0)</f>
+        <v>5</v>
+      </c>
       <c r="G2">
         <v>4</v>
       </c>
       <c r="H2">
         <v>2</v>
       </c>
+      <c r="I2">
+        <f>POWER(G2,H2)</f>
+        <v>16</v>
+      </c>
+      <c r="J2">
+        <f>G2^H2</f>
+        <v>16</v>
+      </c>
       <c r="K2">
         <v>4</v>
       </c>
+      <c r="L2" t="str">
+        <f>ROMAN(K2)</f>
+        <v>IV</v>
+      </c>
       <c r="N2" t="s">
         <v>80</v>
       </c>
+      <c r="O2">
+        <f>_xlfn.ARABIC(N2)</f>
+        <v>4</v>
+      </c>
       <c r="Q2">
         <v>4</v>
       </c>
+      <c r="R2" t="str">
+        <f>REPT(Q2,5)</f>
+        <v>44444</v>
+      </c>
+      <c r="S2" t="str">
+        <f>REPT($S$1,Q2)</f>
+        <v>****</v>
+      </c>
       <c r="U2">
         <v>25</v>
       </c>
+      <c r="V2">
+        <f>SQRT(U2)</f>
+        <v>5</v>
+      </c>
       <c r="X2">
         <v>-25</v>
+      </c>
+      <c r="Y2">
+        <f>ABS(X2)</f>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1.6</v>
       </c>
+      <c r="B3">
+        <f t="shared" ref="B3:B10" si="0">INT(A3)</f>
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <f t="shared" ref="C3:C10" si="1">ROUND(A3,0)</f>
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <f t="shared" ref="D3:D10" si="2">ROUNDUP(A3,0)</f>
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <f t="shared" ref="E3:E10" si="3">ROUNDDOWN(A3,0)</f>
+        <v>1</v>
+      </c>
       <c r="G3">
         <v>6</v>
       </c>
       <c r="H3">
         <v>3</v>
       </c>
+      <c r="I3">
+        <f t="shared" ref="I3:I9" si="4">POWER(G3,H3)</f>
+        <v>216</v>
+      </c>
+      <c r="J3">
+        <f t="shared" ref="J3:J9" si="5">G3^H3</f>
+        <v>216</v>
+      </c>
       <c r="K3">
         <v>6</v>
       </c>
+      <c r="L3" t="str">
+        <f t="shared" ref="L3:L9" si="6">ROMAN(K3)</f>
+        <v>VI</v>
+      </c>
       <c r="N3" t="s">
         <v>81</v>
       </c>
+      <c r="O3">
+        <f t="shared" ref="O3:O9" si="7">_xlfn.ARABIC(N3)</f>
+        <v>6</v>
+      </c>
       <c r="Q3">
         <v>6</v>
       </c>
+      <c r="R3" t="str">
+        <f t="shared" ref="R3:R9" si="8">REPT(Q3,5)</f>
+        <v>66666</v>
+      </c>
+      <c r="S3" t="str">
+        <f t="shared" ref="S3:S9" si="9">REPT($S$1,Q3)</f>
+        <v>******</v>
+      </c>
       <c r="U3">
         <v>4</v>
       </c>
+      <c r="V3">
+        <f t="shared" ref="V3:V9" si="10">SQRT(U3)</f>
+        <v>2</v>
+      </c>
       <c r="X3">
         <v>-4</v>
+      </c>
+      <c r="Y3">
+        <f t="shared" ref="Y3:Y9" si="11">ABS(X3)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>5.5</v>
       </c>
+      <c r="B4">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
       <c r="G4">
         <v>2</v>
       </c>
       <c r="H4">
         <v>3</v>
       </c>
+      <c r="I4">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
       <c r="K4">
         <v>2</v>
       </c>
+      <c r="L4" t="str">
+        <f t="shared" si="6"/>
+        <v>II</v>
+      </c>
       <c r="N4" t="s">
         <v>82</v>
       </c>
+      <c r="O4">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
       <c r="Q4">
         <v>2</v>
       </c>
+      <c r="R4" t="str">
+        <f t="shared" si="8"/>
+        <v>22222</v>
+      </c>
+      <c r="S4" t="str">
+        <f t="shared" si="9"/>
+        <v>**</v>
+      </c>
       <c r="U4">
         <v>16</v>
       </c>
+      <c r="V4">
+        <f t="shared" si="10"/>
+        <v>4</v>
+      </c>
       <c r="X4">
         <v>-16</v>
+      </c>
+      <c r="Y4">
+        <f t="shared" si="11"/>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2.8</v>
       </c>
+      <c r="B5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
       <c r="G5">
         <v>8</v>
       </c>
       <c r="H5">
         <v>2</v>
       </c>
+      <c r="I5">
+        <f t="shared" si="4"/>
+        <v>64</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="5"/>
+        <v>64</v>
+      </c>
       <c r="K5">
         <v>8</v>
       </c>
+      <c r="L5" t="str">
+        <f t="shared" si="6"/>
+        <v>VIII</v>
+      </c>
       <c r="N5" t="s">
         <v>83</v>
       </c>
+      <c r="O5">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
       <c r="Q5">
         <v>8</v>
       </c>
+      <c r="R5" t="str">
+        <f t="shared" si="8"/>
+        <v>88888</v>
+      </c>
+      <c r="S5" t="str">
+        <f t="shared" si="9"/>
+        <v>********</v>
+      </c>
       <c r="U5">
         <v>125</v>
       </c>
+      <c r="V5">
+        <f t="shared" si="10"/>
+        <v>11.180339887498949</v>
+      </c>
       <c r="X5">
         <v>-125</v>
+      </c>
+      <c r="Y5">
+        <f t="shared" si="11"/>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>3.4</v>
       </c>
+      <c r="B6">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
       <c r="G6">
         <v>5</v>
       </c>
       <c r="H6">
         <v>2</v>
       </c>
+      <c r="I6">
+        <f t="shared" si="4"/>
+        <v>25</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="5"/>
+        <v>25</v>
+      </c>
       <c r="K6">
         <v>5</v>
       </c>
+      <c r="L6" t="str">
+        <f t="shared" si="6"/>
+        <v>V</v>
+      </c>
       <c r="N6" t="s">
         <v>84</v>
       </c>
+      <c r="O6">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
       <c r="Q6">
         <v>5</v>
       </c>
+      <c r="R6" t="str">
+        <f t="shared" si="8"/>
+        <v>55555</v>
+      </c>
+      <c r="S6" t="str">
+        <f t="shared" si="9"/>
+        <v>*****</v>
+      </c>
       <c r="U6">
         <v>625</v>
       </c>
+      <c r="V6">
+        <f t="shared" si="10"/>
+        <v>25</v>
+      </c>
       <c r="X6">
         <v>-625</v>
+      </c>
+      <c r="Y6">
+        <f t="shared" si="11"/>
+        <v>625</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>5.5</v>
       </c>
+      <c r="B7">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
       <c r="G7">
         <v>9</v>
       </c>
       <c r="H7">
         <v>3</v>
       </c>
+      <c r="I7">
+        <f t="shared" si="4"/>
+        <v>729</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="5"/>
+        <v>729</v>
+      </c>
       <c r="K7">
         <v>9</v>
       </c>
+      <c r="L7" t="str">
+        <f t="shared" si="6"/>
+        <v>IX</v>
+      </c>
       <c r="N7" t="s">
         <v>85</v>
       </c>
+      <c r="O7">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
       <c r="Q7">
         <v>9</v>
       </c>
+      <c r="R7" t="str">
+        <f t="shared" si="8"/>
+        <v>99999</v>
+      </c>
+      <c r="S7" t="str">
+        <f t="shared" si="9"/>
+        <v>*********</v>
+      </c>
       <c r="U7">
         <v>81</v>
       </c>
+      <c r="V7">
+        <f t="shared" si="10"/>
+        <v>9</v>
+      </c>
       <c r="X7">
         <v>-81</v>
+      </c>
+      <c r="Y7">
+        <f t="shared" si="11"/>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>6.3</v>
       </c>
+      <c r="B8">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
       <c r="G8">
         <v>2</v>
       </c>
       <c r="H8">
         <v>3</v>
       </c>
+      <c r="I8">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
       <c r="K8">
         <v>2</v>
       </c>
+      <c r="L8" t="str">
+        <f t="shared" si="6"/>
+        <v>II</v>
+      </c>
       <c r="N8" t="s">
         <v>82</v>
       </c>
+      <c r="O8">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
       <c r="Q8">
         <v>2</v>
       </c>
+      <c r="R8" t="str">
+        <f t="shared" si="8"/>
+        <v>22222</v>
+      </c>
+      <c r="S8" t="str">
+        <f t="shared" si="9"/>
+        <v>**</v>
+      </c>
       <c r="U8">
         <v>36</v>
       </c>
+      <c r="V8">
+        <f t="shared" si="10"/>
+        <v>6</v>
+      </c>
       <c r="X8">
         <v>-36</v>
+      </c>
+      <c r="Y8">
+        <f t="shared" si="11"/>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>2.8</v>
       </c>
+      <c r="B9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
       <c r="G9">
         <v>7</v>
       </c>
       <c r="H9">
         <v>2</v>
       </c>
+      <c r="I9">
+        <f t="shared" si="4"/>
+        <v>49</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="5"/>
+        <v>49</v>
+      </c>
       <c r="K9">
         <v>7</v>
       </c>
+      <c r="L9" t="str">
+        <f t="shared" si="6"/>
+        <v>VII</v>
+      </c>
       <c r="N9" t="s">
         <v>86</v>
       </c>
+      <c r="O9">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
       <c r="Q9">
         <v>7</v>
       </c>
+      <c r="R9" t="str">
+        <f t="shared" si="8"/>
+        <v>77777</v>
+      </c>
+      <c r="S9" t="str">
+        <f t="shared" si="9"/>
+        <v>*******</v>
+      </c>
       <c r="U9">
         <v>49</v>
       </c>
+      <c r="V9">
+        <f t="shared" si="10"/>
+        <v>7</v>
+      </c>
       <c r="X9">
         <v>-49</v>
+      </c>
+      <c r="Y9">
+        <f t="shared" si="11"/>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>5.2</v>
+      </c>
+      <c r="B10">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="B13" t="s">
+        <v>303</v>
+      </c>
+      <c r="C13" t="s">
+        <v>304</v>
+      </c>
+      <c r="D13" t="s">
+        <v>305</v>
+      </c>
+      <c r="E13" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="B14" t="s">
+        <v>307</v>
+      </c>
+      <c r="C14" t="s">
+        <v>308</v>
+      </c>
+      <c r="D14" t="s">
+        <v>309</v>
+      </c>
+      <c r="I14" t="s">
+        <v>310</v>
+      </c>
+      <c r="J14" t="s">
+        <v>311</v>
+      </c>
+      <c r="L14" t="s">
+        <v>312</v>
+      </c>
+      <c r="O14" t="s">
+        <v>313</v>
+      </c>
+      <c r="R14" t="s">
+        <v>314</v>
+      </c>
+      <c r="S14" t="s">
+        <v>315</v>
+      </c>
+      <c r="V14" t="s">
+        <v>316</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="R15" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B17">
+        <v>34.368200000000002</v>
+      </c>
+      <c r="C17">
+        <f>ROUND(B17,2)</f>
+        <v>34.369999999999997</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B18">
+        <v>34.273099999999999</v>
+      </c>
+      <c r="C18">
+        <f>ROUND(B18,2)</f>
+        <v>34.270000000000003</v>
       </c>
     </row>
   </sheetData>

--- a/Basic Practise File.xlsx
+++ b/Basic Practise File.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B134B972-3163-4958-B1B1-E9A2C8E77AD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FF1743C-957B-4771-AD57-DB865751513C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="955" activeTab="5" xr2:uid="{804A284F-30AB-4AA4-80D9-3863464D9C5B}"/>
   </bookViews>
@@ -1903,7 +1903,7 @@
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C11" s="5">
         <f ca="1">TODAY()</f>
-        <v>46150</v>
+        <v>46151</v>
       </c>
     </row>
   </sheetData>
@@ -2019,7 +2019,7 @@
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <f ca="1">TODAY()</f>
-        <v>46150</v>
+        <v>46151</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -3554,7 +3554,7 @@
   <cols>
     <col min="1" max="1" width="14.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="60.54296875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.453125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="14.453125" bestFit="1" customWidth="1"/>
@@ -4068,7 +4068,7 @@
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13">
         <f ca="1">RAND()</f>
-        <v>0.96855091489393363</v>
+        <v>0.85904776021393436</v>
       </c>
       <c r="I13" t="s">
         <v>302</v>

--- a/Basic Practise File.xlsx
+++ b/Basic Practise File.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FF1743C-957B-4771-AD57-DB865751513C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{955ED579-8702-4BB2-8024-54C38A50ACFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="955" activeTab="5" xr2:uid="{804A284F-30AB-4AA4-80D9-3863464D9C5B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="955" activeTab="6" xr2:uid="{804A284F-30AB-4AA4-80D9-3863464D9C5B}"/>
   </bookViews>
   <sheets>
     <sheet name="Introduction" sheetId="13" r:id="rId1"/>
@@ -1903,7 +1903,7 @@
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C11" s="5">
         <f ca="1">TODAY()</f>
-        <v>46151</v>
+        <v>46152</v>
       </c>
     </row>
   </sheetData>
@@ -2019,7 +2019,7 @@
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <f ca="1">TODAY()</f>
-        <v>46151</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -4068,7 +4068,7 @@
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13">
         <f ca="1">RAND()</f>
-        <v>0.85904776021393436</v>
+        <v>9.8085138375416325E-2</v>
       </c>
       <c r="I13" t="s">
         <v>302</v>

--- a/Basic Practise File.xlsx
+++ b/Basic Practise File.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{955ED579-8702-4BB2-8024-54C38A50ACFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11697638-769E-4874-BABF-B3065ABF1C9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="955" activeTab="6" xr2:uid="{804A284F-30AB-4AA4-80D9-3863464D9C5B}"/>
   </bookViews>
@@ -1903,7 +1903,7 @@
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C11" s="5">
         <f ca="1">TODAY()</f>
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
   </sheetData>
@@ -2019,7 +2019,7 @@
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <f ca="1">TODAY()</f>
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -4068,7 +4068,7 @@
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13">
         <f ca="1">RAND()</f>
-        <v>9.8085138375416325E-2</v>
+        <v>0.5022012912003474</v>
       </c>
       <c r="I13" t="s">
         <v>302</v>
@@ -4961,7 +4961,10 @@
       <c r="I3" t="s">
         <v>262</v>
       </c>
-      <c r="J3" s="3"/>
+      <c r="J3" s="3">
+        <f>SUM(G2:G21)</f>
+        <v>184600</v>
+      </c>
       <c r="K3" s="3"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
@@ -4986,7 +4989,10 @@
       <c r="I4" t="s">
         <v>263</v>
       </c>
-      <c r="J4" s="3"/>
+      <c r="J4" s="3">
+        <f>AVERAGE(G2:G21)</f>
+        <v>9230</v>
+      </c>
       <c r="K4" s="3"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
@@ -5014,7 +5020,10 @@
       <c r="I5" t="s">
         <v>264</v>
       </c>
-      <c r="J5" s="3"/>
+      <c r="J5" s="3">
+        <f>MAX(G2:G21)</f>
+        <v>16250</v>
+      </c>
       <c r="K5" s="3"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
@@ -5039,7 +5048,10 @@
       <c r="I6" t="s">
         <v>265</v>
       </c>
-      <c r="J6" s="3"/>
+      <c r="J6" s="3">
+        <f>MIN(G2:G21)</f>
+        <v>4500</v>
+      </c>
       <c r="K6" s="3"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
@@ -5433,7 +5445,7 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations disablePrompts="1" count="3">
+  <dataValidations count="3">
     <dataValidation type="custom" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G21" xr:uid="{5536C0C2-2435-420F-96C7-E3A0CA654505}">
       <formula1>ISNUMBER(G2)</formula1>
     </dataValidation>

--- a/Basic Practise File.xlsx
+++ b/Basic Practise File.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11697638-769E-4874-BABF-B3065ABF1C9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA320710-51B8-4291-A88E-525969E5D8A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="955" activeTab="6" xr2:uid="{804A284F-30AB-4AA4-80D9-3863464D9C5B}"/>
   </bookViews>
@@ -4068,7 +4068,7 @@
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13">
         <f ca="1">RAND()</f>
-        <v>0.5022012912003474</v>
+        <v>0.89502154756786922</v>
       </c>
       <c r="I13" t="s">
         <v>302</v>
@@ -4867,7 +4867,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF840B8A-933F-4454-B6E1-803F16D7713B}">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.54296875" bestFit="1" customWidth="1"/>
@@ -4883,7 +4883,7 @@
     <col min="12" max="12" width="69.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>90</v>
       </c>
@@ -4909,7 +4909,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4936,7 +4936,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="K3" s="3"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4995,7 +4995,7 @@
       </c>
       <c r="K4" s="3"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="K5" s="3"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -5054,7 +5054,7 @@
       </c>
       <c r="K6" s="3"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -5079,8 +5079,12 @@
       <c r="I7" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J7">
+        <f>COUNT(G2:G21)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -5105,11 +5109,19 @@
       <c r="I8" t="s">
         <v>267</v>
       </c>
+      <c r="J8">
+        <f>COUNTA(D2:D21)</f>
+        <v>19</v>
+      </c>
       <c r="L8" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M8">
+        <f>SUMIFS(G2:G21,F2:F21,F2,E2:E21,E20)</f>
+        <v>16250</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -5134,11 +5146,19 @@
       <c r="I9" t="s">
         <v>268</v>
       </c>
+      <c r="J9">
+        <f>COUNTBLANK(C2:C21)</f>
+        <v>3</v>
+      </c>
       <c r="L9" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M9">
+        <f>AVERAGEIFS(G2:G21,F2:F21,F21,E2:E21,E2)</f>
+        <v>8125</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -5166,8 +5186,12 @@
       <c r="L10" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M10">
+        <f>COUNTIFS(F2:F21,F2,E2:E21,E20)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -5190,7 +5214,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -5216,7 +5240,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -5242,7 +5266,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -5268,7 +5292,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -5297,7 +5321,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>

--- a/Basic Practise File.xlsx
+++ b/Basic Practise File.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA320710-51B8-4291-A88E-525969E5D8A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F5BBC6B-32DE-4D4C-8E47-5591D363D02C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="955" activeTab="6" xr2:uid="{804A284F-30AB-4AA4-80D9-3863464D9C5B}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="323">
   <si>
     <t>Employee Name</t>
   </si>
@@ -1005,6 +1005,18 @@
   </si>
   <si>
     <t>5=number of times reption</t>
+  </si>
+  <si>
+    <t>*=rank(g2,fn+f4[g2:g21])</t>
+  </si>
+  <si>
+    <t>Dense rank</t>
+  </si>
+  <si>
+    <t>lowest rank</t>
+  </si>
+  <si>
+    <t>highest rank</t>
   </si>
 </sst>
 </file>
@@ -1903,7 +1915,7 @@
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C11" s="5">
         <f ca="1">TODAY()</f>
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
   </sheetData>
@@ -2019,7 +2031,7 @@
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <f ca="1">TODAY()</f>
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -4068,7 +4080,7 @@
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13">
         <f ca="1">RAND()</f>
-        <v>0.89502154756786922</v>
+        <v>0.86713801203491814</v>
       </c>
       <c r="I13" t="s">
         <v>302</v>
@@ -4867,7 +4879,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF840B8A-933F-4454-B6E1-803F16D7713B}">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.54296875" bestFit="1" customWidth="1"/>
@@ -4932,7 +4944,7 @@
         <v>10000</v>
       </c>
       <c r="H2">
-        <f>RANK(G2,G2:G21)</f>
+        <f>RANK(G2,$G$2:$G$21,)</f>
         <v>8</v>
       </c>
     </row>
@@ -4958,6 +4970,10 @@
       <c r="G3" s="3">
         <v>12000</v>
       </c>
+      <c r="H3">
+        <f t="shared" ref="H3:H21" si="0">RANK(G3,$G$2:$G$21,)</f>
+        <v>3</v>
+      </c>
       <c r="I3" t="s">
         <v>262</v>
       </c>
@@ -4986,6 +5002,10 @@
       <c r="G4" s="3">
         <v>11250</v>
       </c>
+      <c r="H4">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
       <c r="I4" t="s">
         <v>263</v>
       </c>
@@ -5017,6 +5037,10 @@
       <c r="G5" s="3">
         <v>12000</v>
       </c>
+      <c r="H5">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
       <c r="I5" t="s">
         <v>264</v>
       </c>
@@ -5045,6 +5069,10 @@
       <c r="G6" s="3">
         <v>16250</v>
       </c>
+      <c r="H6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="I6" t="s">
         <v>265</v>
       </c>
@@ -5076,6 +5104,10 @@
       <c r="G7" s="3">
         <v>6400</v>
       </c>
+      <c r="H7">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
       <c r="I7" t="s">
         <v>266</v>
       </c>
@@ -5106,6 +5138,10 @@
       <c r="G8" s="3">
         <v>4500</v>
       </c>
+      <c r="H8">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
       <c r="I8" t="s">
         <v>267</v>
       </c>
@@ -5143,6 +5179,10 @@
       <c r="G9" s="3">
         <v>6275</v>
       </c>
+      <c r="H9">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
       <c r="I9" t="s">
         <v>268</v>
       </c>
@@ -5180,6 +5220,10 @@
       <c r="G10" s="3">
         <v>6250</v>
       </c>
+      <c r="H10">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
       <c r="I10" t="s">
         <v>269</v>
       </c>
@@ -5210,6 +5254,10 @@
       <c r="G11" s="3">
         <v>8750</v>
       </c>
+      <c r="H11">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
       <c r="I11" t="s">
         <v>269</v>
       </c>
@@ -5236,6 +5284,10 @@
       <c r="G12" s="3">
         <v>11250</v>
       </c>
+      <c r="H12">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
       <c r="I12" t="s">
         <v>269</v>
       </c>
@@ -5262,6 +5314,10 @@
       <c r="G13" s="3">
         <v>10000</v>
       </c>
+      <c r="H13">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
       <c r="I13" t="s">
         <v>270</v>
       </c>
@@ -5288,6 +5344,10 @@
       <c r="G14" s="3">
         <v>16250</v>
       </c>
+      <c r="H14">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="I14" t="s">
         <v>271</v>
       </c>
@@ -5314,6 +5374,10 @@
       <c r="G15" s="3">
         <v>6400</v>
       </c>
+      <c r="H15">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
       <c r="I15" t="s">
         <v>269</v>
       </c>
@@ -5343,6 +5407,10 @@
       <c r="G16" s="3">
         <v>4500</v>
       </c>
+      <c r="H16">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
       <c r="I16" t="s">
         <v>272</v>
       </c>
@@ -5369,6 +5437,10 @@
       <c r="G17" s="3">
         <v>6275</v>
       </c>
+      <c r="H17">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
       <c r="I17" t="s">
         <v>273</v>
       </c>
@@ -5398,6 +5470,10 @@
       <c r="G18" s="3">
         <v>6250</v>
       </c>
+      <c r="H18">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19">
@@ -5421,6 +5497,10 @@
       <c r="G19" s="3">
         <v>8750</v>
       </c>
+      <c r="H19">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20">
@@ -5444,6 +5524,10 @@
       <c r="G20" s="3">
         <v>11250</v>
       </c>
+      <c r="H20">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21">
@@ -5466,6 +5550,89 @@
       </c>
       <c r="G21" s="3">
         <v>10000</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="H24" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J28" t="s">
+        <v>320</v>
+      </c>
+      <c r="K28" t="s">
+        <v>321</v>
+      </c>
+      <c r="L28" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="H29">
+        <v>3</v>
+      </c>
+      <c r="I29">
+        <f>RANK(H29,$H$29:$H$35,)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="H30">
+        <v>5</v>
+      </c>
+      <c r="I30">
+        <f t="shared" ref="I30:I35" si="1">RANK(H30,$H$29:$H$35,)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="H31">
+        <v>3</v>
+      </c>
+      <c r="I31">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="H32">
+        <v>6</v>
+      </c>
+      <c r="I32">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="8:9" x14ac:dyDescent="0.35">
+      <c r="H33">
+        <v>1</v>
+      </c>
+      <c r="I33">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="8:9" x14ac:dyDescent="0.35">
+      <c r="H34">
+        <v>2</v>
+      </c>
+      <c r="I34">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="8:9" x14ac:dyDescent="0.35">
+      <c r="H35">
+        <v>6</v>
+      </c>
+      <c r="I35">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Basic Practise File.xlsx
+++ b/Basic Practise File.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F5BBC6B-32DE-4D4C-8E47-5591D363D02C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1ADBAB7-C355-41AA-8CF6-6CD4AA900AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="955" activeTab="6" xr2:uid="{804A284F-30AB-4AA4-80D9-3863464D9C5B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="955" firstSheet="5" activeTab="10" xr2:uid="{804A284F-30AB-4AA4-80D9-3863464D9C5B}"/>
   </bookViews>
   <sheets>
     <sheet name="Introduction" sheetId="13" r:id="rId1"/>
@@ -29,6 +29,9 @@
     <sheet name="Text To Dolumn" sheetId="14" r:id="rId14"/>
     <sheet name="Flash Fill" sheetId="15" r:id="rId15"/>
   </sheets>
+  <definedNames>
+    <definedName name="salary">'Naming Range'!$B$2:$B$14</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -47,8 +50,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="337">
   <si>
     <t>Employee Name</t>
   </si>
@@ -1017,6 +1042,48 @@
   </si>
   <si>
     <t>highest rank</t>
+  </si>
+  <si>
+    <t>*=g5*(fn+f4[j2])</t>
+  </si>
+  <si>
+    <t>*=B$1*$A2</t>
+  </si>
+  <si>
+    <t>select b2:b14</t>
+  </si>
+  <si>
+    <t>then go to formulas</t>
+  </si>
+  <si>
+    <t>there select name manager</t>
+  </si>
+  <si>
+    <t>there select new</t>
+  </si>
+  <si>
+    <t>type a name</t>
+  </si>
+  <si>
+    <t>select the scope</t>
+  </si>
+  <si>
+    <t>*=today()</t>
+  </si>
+  <si>
+    <t>*=now()</t>
+  </si>
+  <si>
+    <t>*=now()-today()</t>
+  </si>
+  <si>
+    <t>click ok</t>
+  </si>
+  <si>
+    <t>then close</t>
+  </si>
+  <si>
+    <t>type =salary</t>
   </si>
 </sst>
 </file>
@@ -1073,7 +1140,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1089,6 +1156,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1665,14 +1734,16 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{970C42C5-F580-424C-94EB-DB4798F8F215}">
   <sheetPr codeName="Sheet11"/>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1680,7 +1751,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1688,7 +1759,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>132</v>
       </c>
@@ -1698,8 +1769,12 @@
       <c r="E3" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F3">
+        <f>SUM(salary)</f>
+        <v>131175</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>123</v>
       </c>
@@ -1709,8 +1784,16 @@
       <c r="E4" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F4">
+        <f>AVERAGE(salary)</f>
+        <v>10090.384615384615</v>
+      </c>
+      <c r="I4" t="e" cm="1">
+        <f t="array" ref="I4">names</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1720,8 +1803,12 @@
       <c r="E5" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F5">
+        <f>MAX(salary)</f>
+        <v>16250</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1731,8 +1818,12 @@
       <c r="E6" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F6">
+        <f>MIN(salary)</f>
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>125</v>
       </c>
@@ -1742,8 +1833,12 @@
       <c r="E7" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F7">
+        <f>COUNT(salary)</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1751,7 +1846,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>1</v>
       </c>
@@ -1759,7 +1854,7 @@
         <v>6275</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>137</v>
       </c>
@@ -1767,7 +1862,7 @@
         <v>6250</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -1775,7 +1870,7 @@
         <v>8750</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -1783,7 +1878,7 @@
         <v>11250</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>126</v>
       </c>
@@ -1791,11 +1886,120 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>3</v>
       </c>
       <c r="B14">
+        <v>16250</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="D15" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="D16" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="17" spans="4:6" x14ac:dyDescent="0.35">
+      <c r="D17" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="18" spans="4:6" x14ac:dyDescent="0.35">
+      <c r="D18" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="19" spans="4:6" x14ac:dyDescent="0.35">
+      <c r="D19" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="20" spans="4:6" x14ac:dyDescent="0.35">
+      <c r="D20" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="21" spans="4:6" x14ac:dyDescent="0.35">
+      <c r="D21" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="22" spans="4:6" x14ac:dyDescent="0.35">
+      <c r="D22" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="23" spans="4:6" x14ac:dyDescent="0.35">
+      <c r="D23" t="s">
+        <v>336</v>
+      </c>
+      <c r="F23" cm="1">
+        <f t="array" ref="F23:F35">salary</f>
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="24" spans="4:6" x14ac:dyDescent="0.35">
+      <c r="F24">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="25" spans="4:6" x14ac:dyDescent="0.35">
+      <c r="F25">
+        <v>11250</v>
+      </c>
+    </row>
+    <row r="26" spans="4:6" x14ac:dyDescent="0.35">
+      <c r="F26">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="27" spans="4:6" x14ac:dyDescent="0.35">
+      <c r="F27">
+        <v>16250</v>
+      </c>
+    </row>
+    <row r="28" spans="4:6" x14ac:dyDescent="0.35">
+      <c r="F28">
+        <v>6400</v>
+      </c>
+    </row>
+    <row r="29" spans="4:6" x14ac:dyDescent="0.35">
+      <c r="F29">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="30" spans="4:6" x14ac:dyDescent="0.35">
+      <c r="F30">
+        <v>6275</v>
+      </c>
+    </row>
+    <row r="31" spans="4:6" x14ac:dyDescent="0.35">
+      <c r="F31">
+        <v>6250</v>
+      </c>
+    </row>
+    <row r="32" spans="4:6" x14ac:dyDescent="0.35">
+      <c r="F32">
+        <v>8750</v>
+      </c>
+    </row>
+    <row r="33" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F33">
+        <v>11250</v>
+      </c>
+    </row>
+    <row r="34" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F34">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="35" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F35">
         <v>16250</v>
       </c>
     </row>
@@ -1818,102 +2022,146 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0575E817-D8B3-476C-80D6-0F216A09C9A3}">
   <sheetPr codeName="Sheet12"/>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="15.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.81640625" customWidth="1"/>
+    <col min="4" max="4" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="10.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C1" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="D1" t="s">
         <v>178</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>180</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>181</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>179</v>
       </c>
       <c r="B2" t="s">
         <v>173</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="5">
+        <v>46154</v>
+      </c>
+      <c r="D2" s="7">
         <v>0.61117256944271503</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E2" s="7">
+        <f>HOUR(D2)</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>178</v>
       </c>
       <c r="B3" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C3" s="13">
+        <v>0.4909722222222222</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>175</v>
       </c>
-      <c r="C4" s="5"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>331</v>
+      </c>
+      <c r="C4" s="5">
+        <f ca="1">TODAY()</f>
+        <v>46154</v>
+      </c>
+      <c r="D4" s="5"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>176</v>
       </c>
-      <c r="C5" s="6"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
+        <v>332</v>
+      </c>
+      <c r="C5" s="6">
+        <f ca="1">NOW()</f>
+        <v>46154.49739733796</v>
+      </c>
+      <c r="D5" s="6"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>177</v>
       </c>
-      <c r="C6" t="s">
+      <c r="B6" t="s">
+        <v>333</v>
+      </c>
+      <c r="C6" s="7">
+        <f ca="1">NOW()-TODAY()</f>
+        <v>0.49739733796013752</v>
+      </c>
+      <c r="D6" t="s">
         <v>180</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>181</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>182</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="D7">
         <v>14</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>40</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>5</v>
       </c>
-      <c r="F7" s="8"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C10" t="s">
+      <c r="G7" s="8"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B8" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B9" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="D10" t="s">
         <v>179</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>193</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C11" s="5">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="D11" s="5">
         <f ca="1">TODAY()</f>
         <v>46154</v>
       </c>
@@ -4080,7 +4328,7 @@
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13">
         <f ca="1">RAND()</f>
-        <v>0.86713801203491814</v>
+        <v>1.8762222605959722E-2</v>
       </c>
       <c r="I13" t="s">
         <v>302</v>
@@ -5654,7 +5902,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1E003CB-9C90-48F7-903C-0D50835FB35D}">
   <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.81640625" bestFit="1" customWidth="1"/>
@@ -5720,11 +5968,19 @@
       <c r="C5">
         <v>6.7</v>
       </c>
+      <c r="D5">
+        <f>B5*C5</f>
+        <v>154.1</v>
+      </c>
       <c r="F5" t="s">
         <v>155</v>
       </c>
       <c r="G5">
         <v>8900</v>
+      </c>
+      <c r="H5">
+        <f>G5*$J$2</f>
+        <v>890</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -5737,6 +5993,10 @@
       <c r="C6">
         <v>4.5</v>
       </c>
+      <c r="D6">
+        <f t="shared" ref="D6:D11" si="0">B6*C6</f>
+        <v>1993.5</v>
+      </c>
       <c r="E6" s="5"/>
       <c r="F6" t="s">
         <v>157</v>
@@ -5744,6 +6004,10 @@
       <c r="G6">
         <v>45000</v>
       </c>
+      <c r="H6">
+        <f t="shared" ref="H6:H10" si="1">G6*$J$2</f>
+        <v>4500</v>
+      </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
@@ -5755,11 +6019,19 @@
       <c r="C7">
         <v>6.7</v>
       </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>3041.8</v>
+      </c>
       <c r="F7" t="s">
         <v>159</v>
       </c>
       <c r="G7">
         <v>34005</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="1"/>
+        <v>3400.5</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
@@ -5772,11 +6044,19 @@
       <c r="C8">
         <v>8.1999999999999993</v>
       </c>
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>533</v>
+      </c>
       <c r="F8" t="s">
         <v>161</v>
       </c>
       <c r="G8">
         <v>23900</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="1"/>
+        <v>2390</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
@@ -5789,6 +6069,10 @@
       <c r="C9">
         <v>5.5</v>
       </c>
+      <c r="D9">
+        <f t="shared" si="0"/>
+        <v>187</v>
+      </c>
       <c r="E9" s="5"/>
       <c r="F9" t="s">
         <v>163</v>
@@ -5796,6 +6080,10 @@
       <c r="G9">
         <v>32000</v>
       </c>
+      <c r="H9">
+        <f t="shared" si="1"/>
+        <v>3200</v>
+      </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
@@ -5807,11 +6095,19 @@
       <c r="C10">
         <v>3.8</v>
       </c>
+      <c r="D10">
+        <f t="shared" si="0"/>
+        <v>171</v>
+      </c>
       <c r="F10" t="s">
         <v>165</v>
       </c>
       <c r="G10">
         <v>12000</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="1"/>
+        <v>1200</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
@@ -5823,6 +6119,15 @@
       </c>
       <c r="C11">
         <v>7.4</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="0"/>
+        <v>236.8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="H13" t="s">
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -5837,10 +6142,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBBF0B49-4E0A-4B05-8FA5-188D814BEFF8}">
   <sheetPr codeName="Sheet10"/>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="5" max="5" width="10.08984375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A1">
         <v>1</v>
       </c>
@@ -5872,49 +6180,434 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B2">
+        <f>B$1*$A2</f>
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <f t="shared" ref="C2:J2" si="0">C$1*$A2</f>
+        <v>6</v>
+      </c>
+      <c r="D2">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="E2">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="F2">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="G2">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="H2">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="I2">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="J2">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B3">
+        <f t="shared" ref="B3:J10" si="1">B$1*$A3</f>
+        <v>6</v>
+      </c>
+      <c r="C3">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="D3">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="E3">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="F3">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="G3">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="H3">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="I3">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="J3">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B4">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="G4">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B5">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="R5" cm="1">
+        <f t="array" ref="R5:R17">salary</f>
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B6">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+      <c r="R6">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B7">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="1"/>
+        <v>56</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="1"/>
+        <v>63</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+      <c r="R7">
+        <v>11250</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B8">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="1"/>
+        <v>56</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="1"/>
+        <v>64</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="1"/>
+        <v>72</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="R8">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>9</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B9">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="1"/>
+        <v>63</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="1"/>
+        <v>72</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="1"/>
+        <v>81</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
+      <c r="P9" t="e" cm="1">
+        <f t="array" ref="P9">names</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="R9">
+        <v>16250</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>10</v>
+      </c>
+      <c r="B10">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="R10">
+        <v>6400</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="R11">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="R12">
+        <v>6275</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="R13">
+        <v>6250</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="R14">
+        <v>8750</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="R15">
+        <v>11250</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="E16" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="R16">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="17" spans="18:18" x14ac:dyDescent="0.35">
+      <c r="R17">
+        <v>16250</v>
       </c>
     </row>
   </sheetData>

--- a/Basic Practise File.xlsx
+++ b/Basic Practise File.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1ADBAB7-C355-41AA-8CF6-6CD4AA900AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="955" firstSheet="5" activeTab="10" xr2:uid="{804A284F-30AB-4AA4-80D9-3863464D9C5B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="955" firstSheet="5" activeTab="7" xr2:uid="{804A284F-30AB-4AA4-80D9-3863464D9C5B}"/>
   </bookViews>
   <sheets>
     <sheet name="Introduction" sheetId="13" r:id="rId1"/>

--- a/Basic Practise File.xlsx
+++ b/Basic Practise File.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1ADBAB7-C355-41AA-8CF6-6CD4AA900AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5E79BCD-8776-4227-AD27-BA11B573A9D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="955" firstSheet="5" activeTab="7" xr2:uid="{804A284F-30AB-4AA4-80D9-3863464D9C5B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="955" firstSheet="5" activeTab="10" xr2:uid="{804A284F-30AB-4AA4-80D9-3863464D9C5B}"/>
   </bookViews>
   <sheets>
     <sheet name="Introduction" sheetId="13" r:id="rId1"/>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="C5" s="6">
         <f ca="1">NOW()</f>
-        <v>46154.49739733796</v>
+        <v>46154.527493171299</v>
       </c>
       <c r="D5" s="6"/>
     </row>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="C6" s="7">
         <f ca="1">NOW()-TODAY()</f>
-        <v>0.49739733796013752</v>
+        <v>0.52749317129928386</v>
       </c>
       <c r="D6" t="s">
         <v>180</v>
@@ -4328,7 +4328,7 @@
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13">
         <f ca="1">RAND()</f>
-        <v>1.8762222605959722E-2</v>
+        <v>0.14223619048714475</v>
       </c>
       <c r="I13" t="s">
         <v>302</v>

--- a/Basic Practise File.xlsx
+++ b/Basic Practise File.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5E79BCD-8776-4227-AD27-BA11B573A9D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D6FDCDC-A37F-4875-A373-4966B9CA2DDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="955" firstSheet="5" activeTab="10" xr2:uid="{804A284F-30AB-4AA4-80D9-3863464D9C5B}"/>
   </bookViews>
@@ -1153,10 +1153,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -2061,9 +2061,17 @@
       <c r="D2" s="7">
         <v>0.61117256944271503</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="14">
         <f>HOUR(D2)</f>
         <v>14</v>
+      </c>
+      <c r="F2">
+        <f>MINUTE(D2)</f>
+        <v>40</v>
+      </c>
+      <c r="G2">
+        <f>SECOND(D2)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -2073,7 +2081,7 @@
       <c r="B3" t="s">
         <v>174</v>
       </c>
-      <c r="C3" s="13">
+      <c r="C3" s="12">
         <v>0.4909722222222222</v>
       </c>
     </row>
@@ -2086,7 +2094,7 @@
       </c>
       <c r="C4" s="5">
         <f ca="1">TODAY()</f>
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="D4" s="5"/>
     </row>
@@ -2099,7 +2107,7 @@
       </c>
       <c r="C5" s="6">
         <f ca="1">NOW()</f>
-        <v>46154.527493171299</v>
+        <v>46155.007678125003</v>
       </c>
       <c r="D5" s="6"/>
     </row>
@@ -2112,7 +2120,7 @@
       </c>
       <c r="C6" s="7">
         <f ca="1">NOW()-TODAY()</f>
-        <v>0.52749317129928386</v>
+        <v>7.678125002712477E-3</v>
       </c>
       <c r="D6" t="s">
         <v>180</v>
@@ -2145,7 +2153,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B9" s="14">
+      <c r="B9">
         <v>1</v>
       </c>
     </row>
@@ -2163,7 +2171,7 @@
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D11" s="5">
         <f ca="1">TODAY()</f>
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
   </sheetData>
@@ -2279,7 +2287,7 @@
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <f ca="1">TODAY()</f>
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -4328,7 +4336,7 @@
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13">
         <f ca="1">RAND()</f>
-        <v>0.14223619048714475</v>
+        <v>0.65154555778481449</v>
       </c>
       <c r="I13" t="s">
         <v>302</v>
@@ -4340,12 +4348,12 @@
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="13" t="s">
         <v>294</v>
       </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5923,17 +5931,17 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="F3" s="12" t="s">
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="F3" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">

--- a/Basic Practise File.xlsx
+++ b/Basic Practise File.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D6FDCDC-A37F-4875-A373-4966B9CA2DDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{313E3496-8BF2-4437-B75C-E7AEBB6F0947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="955" firstSheet="5" activeTab="10" xr2:uid="{804A284F-30AB-4AA4-80D9-3863464D9C5B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="955" firstSheet="5" activeTab="12" xr2:uid="{804A284F-30AB-4AA4-80D9-3863464D9C5B}"/>
   </bookViews>
   <sheets>
     <sheet name="Introduction" sheetId="13" r:id="rId1"/>
@@ -1140,7 +1140,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1157,7 +1157,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2061,7 +2060,7 @@
       <c r="D2" s="7">
         <v>0.61117256944271503</v>
       </c>
-      <c r="E2" s="14">
+      <c r="E2">
         <f>HOUR(D2)</f>
         <v>14</v>
       </c>
@@ -2107,7 +2106,7 @@
       </c>
       <c r="C5" s="6">
         <f ca="1">NOW()</f>
-        <v>46155.007678125003</v>
+        <v>46155.575059259259</v>
       </c>
       <c r="D5" s="6"/>
     </row>
@@ -2120,7 +2119,7 @@
       </c>
       <c r="C6" s="7">
         <f ca="1">NOW()-TODAY()</f>
-        <v>7.678125002712477E-3</v>
+        <v>0.57505925925943302</v>
       </c>
       <c r="D6" t="s">
         <v>180</v>
@@ -2268,20 +2267,132 @@
       <c r="A2">
         <v>34</v>
       </c>
+      <c r="B2" t="b" cm="1">
+        <f t="array" aca="1" ref="B2:B14" ca="1">ISTEXT(A2:A14)</f>
+        <v>0</v>
+      </c>
+      <c r="C2" t="b" cm="1">
+        <f t="array" aca="1" ref="C2:C14" ca="1">ISNONTEXT(A2:A14)</f>
+        <v>1</v>
+      </c>
+      <c r="D2" t="b" cm="1">
+        <f t="array" aca="1" ref="D2:D14" ca="1">ISNUMBER(A2:A14)</f>
+        <v>1</v>
+      </c>
+      <c r="E2" t="b">
+        <f>ISEVEN(A2)</f>
+        <v>1</v>
+      </c>
+      <c r="F2" t="b">
+        <f>ISODD(A2)</f>
+        <v>0</v>
+      </c>
+      <c r="G2" t="b">
+        <f>_xlfn.ISFORMULA(A2)</f>
+        <v>0</v>
+      </c>
+      <c r="H2" t="b">
+        <f>ISLOGICAL(A2)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>54</v>
       </c>
+      <c r="B3" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="C3" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="D3" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="E3" t="b">
+        <f t="shared" ref="E3:E14" si="0">ISEVEN(A3)</f>
+        <v>1</v>
+      </c>
+      <c r="F3" t="b">
+        <f t="shared" ref="F3:F14" si="1">ISODD(A3)</f>
+        <v>0</v>
+      </c>
+      <c r="G3" t="b">
+        <f t="shared" ref="G3:G14" si="2">_xlfn.ISFORMULA(A3)</f>
+        <v>0</v>
+      </c>
+      <c r="H3" t="b">
+        <f t="shared" ref="H3:H14" si="3">ISLOGICAL(A3)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>33</v>
       </c>
+      <c r="B4" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="C4" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="D4" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="E4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F4" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="G4" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H4" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>55</v>
+      </c>
+      <c r="B5" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="C5" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="D5" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="E5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F5" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="G5" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H5" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -2289,24 +2400,164 @@
         <f ca="1">TODAY()</f>
         <v>46155</v>
       </c>
+      <c r="B6" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="C6" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="D6" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="E6" t="b">
+        <f t="shared" ca="1" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F6" t="b">
+        <f t="shared" ca="1" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="G6" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="H6" t="b">
+        <f t="shared" ca="1" si="3"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>190</v>
       </c>
+      <c r="B7" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="C7" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="D7" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="E7" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F7" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G7" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H7" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>23</v>
       </c>
+      <c r="B8" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="C8" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="D8" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="E8" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F8" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="G8" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H8" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>191</v>
       </c>
+      <c r="B9" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="C9" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="D9" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="E9" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F9" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G9" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H9" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="b">
+        <v>1</v>
+      </c>
+      <c r="B10" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="C10" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="D10" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="E10" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F10" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G10" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H10" t="b">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -2314,20 +2565,132 @@
       <c r="A11">
         <v>89</v>
       </c>
+      <c r="B11" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="C11" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="D11" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="E11" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F11" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="G11" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H11" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>23</v>
       </c>
+      <c r="B12" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="C12" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="D12" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="E12" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F12" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="G12" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H12" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="b">
         <v>0</v>
       </c>
+      <c r="B13" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="C13" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="D13" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="E13" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F13" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G13" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H13" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>52</v>
+      </c>
+      <c r="B14" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
+      <c r="C14" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="D14" t="b">
+        <f ca="1"/>
+        <v>1</v>
+      </c>
+      <c r="E14" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F14" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G14" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H14" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4336,7 +4699,7 @@
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13">
         <f ca="1">RAND()</f>
-        <v>0.65154555778481449</v>
+        <v>0.51938537176530408</v>
       </c>
       <c r="I13" t="s">
         <v>302</v>

--- a/Basic Practise File.xlsx
+++ b/Basic Practise File.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{313E3496-8BF2-4437-B75C-E7AEBB6F0947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23666977-709B-459C-833A-19575F553DE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="955" firstSheet="5" activeTab="12" xr2:uid="{804A284F-30AB-4AA4-80D9-3863464D9C5B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="955" firstSheet="5" activeTab="10" xr2:uid="{804A284F-30AB-4AA4-80D9-3863464D9C5B}"/>
   </bookViews>
   <sheets>
     <sheet name="Introduction" sheetId="13" r:id="rId1"/>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="C4" s="5">
         <f ca="1">TODAY()</f>
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="D4" s="5"/>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="C5" s="6">
         <f ca="1">NOW()</f>
-        <v>46155.575059259259</v>
+        <v>46157.43294583333</v>
       </c>
       <c r="D5" s="6"/>
     </row>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="C6" s="7">
         <f ca="1">NOW()-TODAY()</f>
-        <v>0.57505925925943302</v>
+        <v>0.43294583333045011</v>
       </c>
       <c r="D6" t="s">
         <v>180</v>
@@ -2170,7 +2170,15 @@
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D11" s="5">
         <f ca="1">TODAY()</f>
-        <v>46155</v>
+        <v>46157</v>
+      </c>
+      <c r="E11">
+        <f ca="1">WEEKDAY(D11)</f>
+        <v>6</v>
+      </c>
+      <c r="F11">
+        <f ca="1">WEEKNUM(D11)</f>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -2398,7 +2406,7 @@
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <f ca="1">TODAY()</f>
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="B6" t="b">
         <f ca="1"/>
@@ -4699,7 +4707,7 @@
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13">
         <f ca="1">RAND()</f>
-        <v>0.51938537176530408</v>
+        <v>0.17304492283351491</v>
       </c>
       <c r="I13" t="s">
         <v>302</v>

--- a/Basic Practise File.xlsx
+++ b/Basic Practise File.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23666977-709B-459C-833A-19575F553DE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64130EE8-03A7-4F4C-9026-546503E5033B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="955" firstSheet="5" activeTab="10" xr2:uid="{804A284F-30AB-4AA4-80D9-3863464D9C5B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="955" firstSheet="6" activeTab="11" xr2:uid="{804A284F-30AB-4AA4-80D9-3863464D9C5B}"/>
   </bookViews>
   <sheets>
     <sheet name="Introduction" sheetId="13" r:id="rId1"/>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="440">
   <si>
     <t>Employee Name</t>
   </si>
@@ -780,48 +780,12 @@
     <t>GA-05-AP-3456</t>
   </si>
   <si>
-    <t>Anjali ,Thakur</t>
-  </si>
-  <si>
-    <t>Jharna ,Biswal</t>
-  </si>
-  <si>
-    <t>Prakash#Dutta</t>
-  </si>
-  <si>
-    <t>Manisha;Guha</t>
-  </si>
-  <si>
-    <t>Arjun,JAiN</t>
-  </si>
-  <si>
-    <t>Arjun#Kapoor</t>
-  </si>
-  <si>
-    <t>R#Vasu,Muthanna</t>
-  </si>
-  <si>
-    <t>"Priya AgarwaL"</t>
-  </si>
-  <si>
-    <t>"Ajay Kumar"</t>
-  </si>
-  <si>
-    <t>Sanjay;Gupta</t>
-  </si>
-  <si>
     <t>Example-1</t>
   </si>
   <si>
     <t>Example-2</t>
   </si>
   <si>
-    <t>Example-3</t>
-  </si>
-  <si>
-    <t>Example-4</t>
-  </si>
-  <si>
     <t>Linear</t>
   </si>
   <si>
@@ -1084,6 +1048,351 @@
   </si>
   <si>
     <t>type =salary</t>
+  </si>
+  <si>
+    <t>select the required cells</t>
+  </si>
+  <si>
+    <t>then click fill in home tab</t>
+  </si>
+  <si>
+    <t>then select series</t>
+  </si>
+  <si>
+    <t>then enter the stop count</t>
+  </si>
+  <si>
+    <t>select growth</t>
+  </si>
+  <si>
+    <t>enter the step count</t>
+  </si>
+  <si>
+    <t>then enter the step count</t>
+  </si>
+  <si>
+    <t>select date</t>
+  </si>
+  <si>
+    <t>then select the day units - month</t>
+  </si>
+  <si>
+    <t>then select the day units to year</t>
+  </si>
+  <si>
+    <t>enter the step value</t>
+  </si>
+  <si>
+    <t>select the day unit to weekdays</t>
+  </si>
+  <si>
+    <t>Monday</t>
+  </si>
+  <si>
+    <t>Tuesday</t>
+  </si>
+  <si>
+    <t>Wednesday</t>
+  </si>
+  <si>
+    <t>Thursday</t>
+  </si>
+  <si>
+    <t>Friday</t>
+  </si>
+  <si>
+    <t>Saturday</t>
+  </si>
+  <si>
+    <t>Sunday</t>
+  </si>
+  <si>
+    <t>Jan</t>
+  </si>
+  <si>
+    <t>Feb</t>
+  </si>
+  <si>
+    <t>Mar</t>
+  </si>
+  <si>
+    <t>Apr</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>Jun</t>
+  </si>
+  <si>
+    <t>Jul</t>
+  </si>
+  <si>
+    <t>Aug</t>
+  </si>
+  <si>
+    <t>Sep</t>
+  </si>
+  <si>
+    <t>Oct</t>
+  </si>
+  <si>
+    <t>Nov</t>
+  </si>
+  <si>
+    <t>Dec</t>
+  </si>
+  <si>
+    <t>table</t>
+  </si>
+  <si>
+    <t>chair</t>
+  </si>
+  <si>
+    <t>board</t>
+  </si>
+  <si>
+    <t>wall</t>
+  </si>
+  <si>
+    <t>room</t>
+  </si>
+  <si>
+    <t>screen</t>
+  </si>
+  <si>
+    <t>projector</t>
+  </si>
+  <si>
+    <t>just enter the first character</t>
+  </si>
+  <si>
+    <t>then drag it</t>
+  </si>
+  <si>
+    <t>go to files</t>
+  </si>
+  <si>
+    <t>click option</t>
+  </si>
+  <si>
+    <t>click advanced</t>
+  </si>
+  <si>
+    <t>scroll dowun to botton of advanced</t>
+  </si>
+  <si>
+    <t>KA</t>
+  </si>
+  <si>
+    <t>KP</t>
+  </si>
+  <si>
+    <t>MH</t>
+  </si>
+  <si>
+    <t>AP</t>
+  </si>
+  <si>
+    <t>TN</t>
+  </si>
+  <si>
+    <t>RD</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>TS</t>
+  </si>
+  <si>
+    <t>BA</t>
+  </si>
+  <si>
+    <t>KL</t>
+  </si>
+  <si>
+    <t>ST</t>
+  </si>
+  <si>
+    <t>WB</t>
+  </si>
+  <si>
+    <t>CG</t>
+  </si>
+  <si>
+    <t>UP</t>
+  </si>
+  <si>
+    <t>OR</t>
+  </si>
+  <si>
+    <t>KN</t>
+  </si>
+  <si>
+    <t>DL</t>
+  </si>
+  <si>
+    <t>EG</t>
+  </si>
+  <si>
+    <t>GA</t>
+  </si>
+  <si>
+    <t>selec the required data field</t>
+  </si>
+  <si>
+    <t>the select the data</t>
+  </si>
+  <si>
+    <t>then click text to columns</t>
+  </si>
+  <si>
+    <t>Thakur</t>
+  </si>
+  <si>
+    <t>Muthanna</t>
+  </si>
+  <si>
+    <t>Gupta</t>
+  </si>
+  <si>
+    <t>select the delimited</t>
+  </si>
+  <si>
+    <t>then click next</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Priya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AgarwaL </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ajay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kumar </t>
+  </si>
+  <si>
+    <t>KA05KP8562</t>
+  </si>
+  <si>
+    <t>MH05AP9845</t>
+  </si>
+  <si>
+    <t>TN10RD9878</t>
+  </si>
+  <si>
+    <t>AP10NA2378</t>
+  </si>
+  <si>
+    <t>TS04BA9567</t>
+  </si>
+  <si>
+    <t>KL07ST8923</t>
+  </si>
+  <si>
+    <t>WB11CG5679</t>
+  </si>
+  <si>
+    <t>UP09ST7453</t>
+  </si>
+  <si>
+    <t>OR06KN4598</t>
+  </si>
+  <si>
+    <t>DL03EG8345</t>
+  </si>
+  <si>
+    <t>GA05AP3456</t>
+  </si>
+  <si>
+    <t>then select the delimeters</t>
+  </si>
+  <si>
+    <t>then click ok</t>
+  </si>
+  <si>
+    <t>if you want any text qualifers</t>
+  </si>
+  <si>
+    <t>then</t>
+  </si>
+  <si>
+    <t>jp kumar</t>
+  </si>
+  <si>
+    <t>anjali thakur</t>
+  </si>
+  <si>
+    <t>priya agarwal</t>
+  </si>
+  <si>
+    <t>r vasu</t>
+  </si>
+  <si>
+    <t>sanjay gupta</t>
+  </si>
+  <si>
+    <t>jharna biswal</t>
+  </si>
+  <si>
+    <t>prakash dutta</t>
+  </si>
+  <si>
+    <t>manisha guha</t>
+  </si>
+  <si>
+    <t>arjun jain</t>
+  </si>
+  <si>
+    <t>arjun kapoor</t>
+  </si>
+  <si>
+    <t>write the name in lower case</t>
+  </si>
+  <si>
+    <t>JK123@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>AT123@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>PA123@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>RV123@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>SG123@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>JB123@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>PD123@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>MG123@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>AJ123@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>AK123@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>edit custom list</t>
+  </si>
+  <si>
+    <t>select the required text or series</t>
+  </si>
+  <si>
+    <t>then click add</t>
+  </si>
+  <si>
+    <t>click of</t>
   </si>
 </sst>
 </file>
@@ -1094,7 +1403,7 @@
     <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00;[Red]&quot;₹&quot;\ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1114,6 +1423,12 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1895,47 +2210,47 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="D15" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="D16" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
     </row>
     <row r="17" spans="4:6" x14ac:dyDescent="0.35">
       <c r="D17" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
     </row>
     <row r="18" spans="4:6" x14ac:dyDescent="0.35">
       <c r="D18" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
     </row>
     <row r="19" spans="4:6" x14ac:dyDescent="0.35">
       <c r="D19" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
     </row>
     <row r="20" spans="4:6" x14ac:dyDescent="0.35">
       <c r="D20" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
     </row>
     <row r="21" spans="4:6" x14ac:dyDescent="0.35">
       <c r="D21" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
     </row>
     <row r="22" spans="4:6" x14ac:dyDescent="0.35">
       <c r="D22" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
     </row>
     <row r="23" spans="4:6" x14ac:dyDescent="0.35">
       <c r="D23" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="F23" cm="1">
         <f t="array" ref="F23:F35">salary</f>
@@ -2089,7 +2404,7 @@
         <v>175</v>
       </c>
       <c r="B4" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="C4" s="5">
         <f ca="1">TODAY()</f>
@@ -2102,11 +2417,11 @@
         <v>176</v>
       </c>
       <c r="B5" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="C5" s="6">
         <f ca="1">NOW()</f>
-        <v>46157.43294583333</v>
+        <v>46157.946482754633</v>
       </c>
       <c r="D5" s="6"/>
     </row>
@@ -2115,11 +2430,11 @@
         <v>177</v>
       </c>
       <c r="B6" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="C6" s="7">
         <f ca="1">NOW()-TODAY()</f>
-        <v>0.43294583333045011</v>
+        <v>0.94648275463259779</v>
       </c>
       <c r="D6" t="s">
         <v>180</v>
@@ -2189,45 +2504,537 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6185B783-F349-4D8D-9FAF-8BC1D13FF235}">
   <sheetPr codeName="Sheet13"/>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.81640625" customWidth="1"/>
-    <col min="2" max="2" width="20.08984375" customWidth="1"/>
+    <col min="2" max="2" width="22.6328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.6328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.08984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="B1" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="C1" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="D1" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="E1" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="F1" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="G1" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="H1" t="s">
         <v>193</v>
       </c>
       <c r="J1" t="s">
-        <v>254</v>
+        <v>242</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2" s="5">
+        <v>46157</v>
+      </c>
+      <c r="F2" s="5">
+        <v>46157</v>
+      </c>
+      <c r="G2" s="5">
+        <f ca="1">TODAY()</f>
+        <v>46157</v>
+      </c>
+      <c r="H2" s="5">
+        <f ca="1">TODAY()</f>
+        <v>46157</v>
+      </c>
+      <c r="J2" t="s">
+        <v>337</v>
+      </c>
+      <c r="L2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>4</v>
+      </c>
+      <c r="B3">
+        <v>10</v>
+      </c>
+      <c r="C3">
+        <f>C2*4</f>
+        <v>12</v>
+      </c>
+      <c r="D3">
+        <v>12</v>
+      </c>
+      <c r="E3" s="5">
+        <v>46159</v>
+      </c>
+      <c r="F3" s="5">
+        <v>46188</v>
+      </c>
+      <c r="G3" s="5">
+        <v>64420</v>
+      </c>
+      <c r="H3" s="5">
+        <v>46160</v>
+      </c>
+      <c r="J3" t="s">
+        <v>338</v>
+      </c>
+      <c r="L3" t="s">
+        <v>345</v>
+      </c>
+      <c r="N3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>15</v>
+      </c>
+      <c r="C4">
+        <f t="shared" ref="C4:C11" si="0">C3*4</f>
+        <v>48</v>
+      </c>
+      <c r="D4">
+        <v>48</v>
+      </c>
+      <c r="E4" s="5">
+        <v>46161</v>
+      </c>
+      <c r="F4" s="5">
+        <v>46218</v>
+      </c>
+      <c r="G4" s="5">
+        <v>82681</v>
+      </c>
+      <c r="H4" s="5">
+        <v>46161</v>
+      </c>
+      <c r="J4" t="s">
+        <v>339</v>
+      </c>
+      <c r="L4" t="s">
+        <v>346</v>
+      </c>
+      <c r="N4" t="s">
+        <v>357</v>
+      </c>
+      <c r="O4" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>20</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="0"/>
+        <v>192</v>
+      </c>
+      <c r="D5">
+        <v>192</v>
+      </c>
+      <c r="E5" s="5">
+        <v>46163</v>
+      </c>
+      <c r="F5" s="5">
+        <v>46249</v>
+      </c>
+      <c r="G5" s="5">
+        <v>100944</v>
+      </c>
+      <c r="H5" s="5">
+        <v>46162</v>
+      </c>
+      <c r="J5" t="s">
+        <v>340</v>
+      </c>
+      <c r="L5" t="s">
+        <v>347</v>
+      </c>
+      <c r="N5" t="s">
+        <v>358</v>
+      </c>
+      <c r="O5" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>25</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="0"/>
+        <v>768</v>
+      </c>
+      <c r="D6">
+        <v>768</v>
+      </c>
+      <c r="E6" s="5">
+        <v>46165</v>
+      </c>
+      <c r="F6" s="5">
+        <v>46280</v>
+      </c>
+      <c r="G6" s="5">
+        <v>119205</v>
+      </c>
+      <c r="H6" s="5">
+        <v>46163</v>
+      </c>
+      <c r="J6" t="s">
+        <v>341</v>
+      </c>
+      <c r="L6" t="s">
+        <v>348</v>
+      </c>
+      <c r="N6" t="s">
+        <v>361</v>
+      </c>
+      <c r="O6" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>12</v>
+      </c>
+      <c r="B7">
+        <v>30</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="0"/>
+        <v>3072</v>
+      </c>
+      <c r="D7">
+        <v>3072</v>
+      </c>
+      <c r="E7" s="5">
+        <v>46167</v>
+      </c>
+      <c r="F7" s="5">
+        <v>46310</v>
+      </c>
+      <c r="G7" s="5">
+        <v>137468</v>
+      </c>
+      <c r="H7" s="5">
+        <v>46164</v>
+      </c>
+      <c r="J7" t="s">
+        <v>342</v>
+      </c>
+      <c r="L7" t="s">
+        <v>349</v>
+      </c>
+      <c r="N7" t="s">
+        <v>362</v>
+      </c>
+      <c r="O7" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>14</v>
+      </c>
+      <c r="B8">
+        <v>35</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="0"/>
+        <v>12288</v>
+      </c>
+      <c r="D8">
+        <v>12288</v>
+      </c>
+      <c r="E8" s="5">
+        <v>46169</v>
+      </c>
+      <c r="F8" s="5">
+        <v>46341</v>
+      </c>
+      <c r="G8" s="5">
+        <v>155729</v>
+      </c>
+      <c r="H8" s="5">
+        <v>46167</v>
+      </c>
+      <c r="J8" t="s">
+        <v>343</v>
+      </c>
+      <c r="L8" t="s">
+        <v>350</v>
+      </c>
+      <c r="N8" t="s">
+        <v>359</v>
+      </c>
+      <c r="O8" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>16</v>
+      </c>
+      <c r="B9">
+        <v>40</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="0"/>
+        <v>49152</v>
+      </c>
+      <c r="D9">
+        <v>49152</v>
+      </c>
+      <c r="E9" s="5">
+        <v>46171</v>
+      </c>
+      <c r="F9" s="5">
+        <v>46371</v>
+      </c>
+      <c r="G9" s="5">
+        <v>173992</v>
+      </c>
+      <c r="H9" s="5">
+        <v>46168</v>
+      </c>
+      <c r="J9" t="s">
+        <v>337</v>
+      </c>
+      <c r="L9" t="s">
+        <v>351</v>
+      </c>
+      <c r="N9" t="s">
+        <v>360</v>
+      </c>
+      <c r="O9" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>18</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="0"/>
+        <v>196608</v>
+      </c>
+      <c r="D10">
+        <v>196608</v>
+      </c>
+      <c r="E10" s="5">
+        <v>46173</v>
+      </c>
+      <c r="F10" s="5">
+        <v>46402</v>
+      </c>
+      <c r="G10" s="5">
+        <v>192254</v>
+      </c>
+      <c r="H10" s="5">
+        <v>46169</v>
+      </c>
+      <c r="J10" t="s">
+        <v>338</v>
+      </c>
+      <c r="L10" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>20</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="0"/>
+        <v>786432</v>
+      </c>
+      <c r="D11">
+        <v>786432</v>
+      </c>
+      <c r="E11" s="5">
+        <v>46175</v>
+      </c>
+      <c r="F11" s="5">
+        <v>46433</v>
+      </c>
+      <c r="G11" s="5">
+        <v>210517</v>
+      </c>
+      <c r="H11" s="5">
+        <v>46170</v>
+      </c>
+      <c r="J11" t="s">
+        <v>339</v>
+      </c>
+      <c r="L11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="L12" t="s">
+        <v>354</v>
+      </c>
+      <c r="N12" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="B13" t="s">
+        <v>325</v>
+      </c>
+      <c r="L13" t="s">
+        <v>355</v>
+      </c>
+      <c r="N13" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="B14" t="s">
+        <v>326</v>
+      </c>
+      <c r="N14" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="B15" t="s">
+        <v>327</v>
+      </c>
+      <c r="D15" t="s">
+        <v>329</v>
+      </c>
+      <c r="E15" t="s">
+        <v>332</v>
+      </c>
+      <c r="F15" t="s">
+        <v>332</v>
+      </c>
+      <c r="G15" t="s">
+        <v>332</v>
+      </c>
+      <c r="H15" t="s">
+        <v>332</v>
+      </c>
+      <c r="J15" t="s">
+        <v>363</v>
+      </c>
+      <c r="N15" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="B16" t="s">
+        <v>331</v>
+      </c>
+      <c r="D16" t="s">
+        <v>330</v>
+      </c>
+      <c r="E16" t="s">
+        <v>330</v>
+      </c>
+      <c r="F16" t="s">
+        <v>333</v>
+      </c>
+      <c r="G16" t="s">
+        <v>334</v>
+      </c>
+      <c r="H16" t="s">
+        <v>336</v>
+      </c>
+      <c r="J16" t="s">
+        <v>364</v>
+      </c>
+      <c r="N16" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B17" t="s">
+        <v>328</v>
+      </c>
+      <c r="F17" t="s">
+        <v>335</v>
+      </c>
+      <c r="G17" t="s">
+        <v>335</v>
+      </c>
+      <c r="H17" t="s">
+        <v>335</v>
+      </c>
+      <c r="N17" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B18" t="s">
+        <v>322</v>
+      </c>
+      <c r="D18" t="s">
+        <v>322</v>
+      </c>
+      <c r="F18" t="s">
+        <v>322</v>
+      </c>
+      <c r="H18" t="s">
+        <v>322</v>
+      </c>
+      <c r="N18" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="N19" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="N20" t="s">
+        <v>439</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2709,7 +3516,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BBACF5E-B802-4707-BE70-A8315AA524C2}">
   <sheetPr codeName="Sheet15"/>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.54296875" customWidth="1"/>
@@ -2717,7 +3524,7 @@
     <col min="6" max="6" width="16.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>183</v>
       </c>
@@ -2725,92 +3532,492 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>224</v>
       </c>
+      <c r="B2" t="s">
+        <v>369</v>
+      </c>
+      <c r="C2">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E2">
+        <v>8562</v>
+      </c>
       <c r="F2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="G2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>231</v>
       </c>
+      <c r="B3" t="s">
+        <v>371</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3" t="s">
+        <v>372</v>
+      </c>
+      <c r="E3">
+        <v>9845</v>
+      </c>
       <c r="F3" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="G3" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>225</v>
       </c>
+      <c r="B4" t="s">
+        <v>373</v>
+      </c>
+      <c r="C4">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>374</v>
+      </c>
+      <c r="E4">
+        <v>9878</v>
+      </c>
       <c r="F4" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+        <v>396</v>
+      </c>
+      <c r="G4" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>226</v>
       </c>
+      <c r="B5" t="s">
+        <v>372</v>
+      </c>
+      <c r="C5">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>375</v>
+      </c>
+      <c r="E5">
+        <v>2378</v>
+      </c>
       <c r="F5" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+      <c r="G5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>227</v>
       </c>
+      <c r="B6" t="s">
+        <v>376</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
+        <v>377</v>
+      </c>
+      <c r="E6">
+        <v>9567</v>
+      </c>
       <c r="F6" s="9" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+      <c r="G6" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>228</v>
       </c>
+      <c r="B7" t="s">
+        <v>378</v>
+      </c>
+      <c r="C7">
+        <v>7</v>
+      </c>
+      <c r="D7" t="s">
+        <v>379</v>
+      </c>
+      <c r="E7">
+        <v>8923</v>
+      </c>
       <c r="F7" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+        <v>32</v>
+      </c>
+      <c r="G7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>229</v>
       </c>
+      <c r="B8" t="s">
+        <v>380</v>
+      </c>
+      <c r="C8">
+        <v>11</v>
+      </c>
+      <c r="D8" t="s">
+        <v>381</v>
+      </c>
+      <c r="E8">
+        <v>5679</v>
+      </c>
       <c r="F8" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+        <v>34</v>
+      </c>
+      <c r="G8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>230</v>
       </c>
+      <c r="B9" t="s">
+        <v>382</v>
+      </c>
+      <c r="C9">
+        <v>9</v>
+      </c>
+      <c r="D9" t="s">
+        <v>379</v>
+      </c>
+      <c r="E9">
+        <v>7453</v>
+      </c>
       <c r="F9" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+        <v>36</v>
+      </c>
+      <c r="G9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>232</v>
       </c>
+      <c r="B10" t="s">
+        <v>383</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+      <c r="D10" t="s">
+        <v>384</v>
+      </c>
+      <c r="E10">
+        <v>4598</v>
+      </c>
       <c r="F10" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+      <c r="G10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>233</v>
       </c>
+      <c r="B11" t="s">
+        <v>385</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+      <c r="D11" t="s">
+        <v>386</v>
+      </c>
+      <c r="E11">
+        <v>8345</v>
+      </c>
       <c r="F11" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+      <c r="G11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>234</v>
       </c>
+      <c r="B12" t="s">
+        <v>387</v>
+      </c>
+      <c r="C12">
+        <v>5</v>
+      </c>
+      <c r="D12" t="s">
+        <v>372</v>
+      </c>
+      <c r="E12">
+        <v>3456</v>
+      </c>
       <c r="F12" t="s">
-        <v>243</v>
+        <v>398</v>
+      </c>
+      <c r="G12" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>400</v>
+      </c>
+      <c r="B24" t="s">
+        <v>369</v>
+      </c>
+      <c r="C24">
+        <v>5</v>
+      </c>
+      <c r="D24" t="s">
+        <v>370</v>
+      </c>
+      <c r="E24">
+        <v>8562</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>401</v>
+      </c>
+      <c r="B25" t="s">
+        <v>371</v>
+      </c>
+      <c r="C25">
+        <v>5</v>
+      </c>
+      <c r="D25" t="s">
+        <v>372</v>
+      </c>
+      <c r="E25">
+        <v>9845</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>402</v>
+      </c>
+      <c r="B26" t="s">
+        <v>373</v>
+      </c>
+      <c r="C26">
+        <v>10</v>
+      </c>
+      <c r="D26" t="s">
+        <v>374</v>
+      </c>
+      <c r="E26">
+        <v>9878</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>403</v>
+      </c>
+      <c r="B27" t="s">
+        <v>372</v>
+      </c>
+      <c r="C27">
+        <v>10</v>
+      </c>
+      <c r="D27" t="s">
+        <v>375</v>
+      </c>
+      <c r="E27">
+        <v>2378</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>404</v>
+      </c>
+      <c r="B28" t="s">
+        <v>376</v>
+      </c>
+      <c r="C28">
+        <v>4</v>
+      </c>
+      <c r="D28" t="s">
+        <v>377</v>
+      </c>
+      <c r="E28">
+        <v>9567</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>405</v>
+      </c>
+      <c r="B29" t="s">
+        <v>378</v>
+      </c>
+      <c r="C29">
+        <v>7</v>
+      </c>
+      <c r="D29" t="s">
+        <v>379</v>
+      </c>
+      <c r="E29">
+        <v>8923</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>406</v>
+      </c>
+      <c r="B30" t="s">
+        <v>380</v>
+      </c>
+      <c r="C30">
+        <v>11</v>
+      </c>
+      <c r="D30" t="s">
+        <v>381</v>
+      </c>
+      <c r="E30">
+        <v>5679</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>407</v>
+      </c>
+      <c r="B31" t="s">
+        <v>382</v>
+      </c>
+      <c r="C31">
+        <v>9</v>
+      </c>
+      <c r="D31" t="s">
+        <v>379</v>
+      </c>
+      <c r="E31">
+        <v>7453</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>408</v>
+      </c>
+      <c r="B32" t="s">
+        <v>383</v>
+      </c>
+      <c r="C32">
+        <v>6</v>
+      </c>
+      <c r="D32" t="s">
+        <v>384</v>
+      </c>
+      <c r="E32">
+        <v>4598</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>409</v>
+      </c>
+      <c r="B33" t="s">
+        <v>385</v>
+      </c>
+      <c r="C33">
+        <v>3</v>
+      </c>
+      <c r="D33" t="s">
+        <v>386</v>
+      </c>
+      <c r="E33">
+        <v>8345</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>410</v>
+      </c>
+      <c r="B34" t="s">
+        <v>387</v>
+      </c>
+      <c r="C34">
+        <v>5</v>
+      </c>
+      <c r="D34" t="s">
+        <v>372</v>
+      </c>
+      <c r="E34">
+        <v>3456</v>
       </c>
     </row>
   </sheetData>
@@ -2844,17 +4051,13 @@
         <v>42</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>248</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
@@ -2863,7 +4066,15 @@
       <c r="B2" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="11"/>
+      <c r="C2" t="s">
+        <v>415</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>426</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>425</v>
+      </c>
       <c r="F2" s="11"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -2873,6 +4084,12 @@
       <c r="B3" t="s">
         <v>25</v>
       </c>
+      <c r="C3" t="s">
+        <v>416</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>427</v>
+      </c>
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
     </row>
@@ -2883,6 +4100,12 @@
       <c r="B4" t="s">
         <v>27</v>
       </c>
+      <c r="C4" t="s">
+        <v>417</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>428</v>
+      </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
     </row>
@@ -2893,6 +4116,12 @@
       <c r="B5" t="s">
         <v>29</v>
       </c>
+      <c r="C5" t="s">
+        <v>418</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>429</v>
+      </c>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
     </row>
@@ -2903,6 +4132,12 @@
       <c r="B6" t="s">
         <v>31</v>
       </c>
+      <c r="C6" t="s">
+        <v>419</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>430</v>
+      </c>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
     </row>
@@ -2913,6 +4148,12 @@
       <c r="B7" t="s">
         <v>33</v>
       </c>
+      <c r="C7" t="s">
+        <v>420</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>431</v>
+      </c>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
     </row>
@@ -2923,6 +4164,12 @@
       <c r="B8" t="s">
         <v>35</v>
       </c>
+      <c r="C8" t="s">
+        <v>421</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>432</v>
+      </c>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
     </row>
@@ -2933,6 +4180,12 @@
       <c r="B9" t="s">
         <v>37</v>
       </c>
+      <c r="C9" t="s">
+        <v>422</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>433</v>
+      </c>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
     </row>
@@ -2943,6 +4196,12 @@
       <c r="B10" t="s">
         <v>39</v>
       </c>
+      <c r="C10" t="s">
+        <v>423</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>434</v>
+      </c>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
     </row>
@@ -2952,6 +4211,12 @@
       </c>
       <c r="B11" t="s">
         <v>40</v>
+      </c>
+      <c r="C11" t="s">
+        <v>424</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>435</v>
       </c>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
@@ -2962,6 +4227,18 @@
       <formula1>ISTEXT(A1)</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{9229532A-9949-415A-9257-C89E22271426}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{54DA68C0-D37D-4685-9D5D-33F83B9E114E}"/>
+    <hyperlink ref="D4" r:id="rId3" xr:uid="{C4FD7D30-6542-4D10-866B-02B9EDAA0E2E}"/>
+    <hyperlink ref="D5" r:id="rId4" xr:uid="{C35A2C22-0595-4B86-8150-60313D80B370}"/>
+    <hyperlink ref="D6" r:id="rId5" xr:uid="{24D30A5F-1B0C-4083-B47D-F3BB029F3F86}"/>
+    <hyperlink ref="D7" r:id="rId6" xr:uid="{9341BB85-41CC-4AEC-B4C1-26799E2569F0}"/>
+    <hyperlink ref="D8" r:id="rId7" xr:uid="{8661F97C-DE8E-4B1B-A981-48A2B6A2BC4F}"/>
+    <hyperlink ref="D9" r:id="rId8" xr:uid="{FA3FC234-6A08-4197-8A1D-669FFF778540}"/>
+    <hyperlink ref="D10" r:id="rId9" xr:uid="{D8066074-50C8-4620-A70B-6C36E808B0CB}"/>
+    <hyperlink ref="D11" r:id="rId10" xr:uid="{3CCD4A96-CB28-4727-A42A-628CE125AC29}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3004,10 +4281,10 @@
         <v>21</v>
       </c>
       <c r="I1" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="J1" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>41</v>
@@ -3043,7 +4320,7 @@
         <v>50</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="W1" s="1" t="s">
         <v>0</v>
@@ -3471,7 +4748,7 @@
         <v>Sanjay GuptA</v>
       </c>
       <c r="N6" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="O6" t="s">
         <v>5</v>
@@ -3974,48 +5251,48 @@
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.35">
       <c r="P13" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="Q13" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="U13" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -4246,13 +5523,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="B4" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="E4" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="F4" t="str">
         <f t="shared" si="0"/>
@@ -4336,13 +5613,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="B10" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="E10" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="F10" t="str">
         <f t="shared" si="0"/>
@@ -4366,17 +5643,17 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="E13" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="E14" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="E15" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
     </row>
   </sheetData>
@@ -4678,49 +5955,49 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="C11" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="D11" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="E11" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="B12" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="H12" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="I12" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13">
         <f ca="1">RAND()</f>
-        <v>0.17304492283351491</v>
+        <v>0.78148092061372865</v>
       </c>
       <c r="I13" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="13" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -4777,7 +6054,7 @@
         <v>67</v>
       </c>
       <c r="J1" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="K1" t="s">
         <v>56</v>
@@ -4789,7 +6066,7 @@
         <v>56</v>
       </c>
       <c r="O1" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="Q1" t="s">
         <v>56</v>
@@ -5428,56 +6705,56 @@
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="C13" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="D13" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="E13" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="C14" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="D14" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="I14" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="J14" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="L14" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="O14" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="R14" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="S14" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="V14" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="Y14" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.35">
       <c r="R15" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.35">
@@ -5545,7 +6822,7 @@
         <v>94</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
@@ -5602,7 +6879,7 @@
         <v>3</v>
       </c>
       <c r="I3" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="J3" s="3">
         <f>SUM(G2:G21)</f>
@@ -5634,7 +6911,7 @@
         <v>5</v>
       </c>
       <c r="I4" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="J4" s="3">
         <f>AVERAGE(G2:G21)</f>
@@ -5669,7 +6946,7 @@
         <v>3</v>
       </c>
       <c r="I5" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="J5" s="3">
         <f>MAX(G2:G21)</f>
@@ -5701,7 +6978,7 @@
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="J6" s="3">
         <f>MIN(G2:G21)</f>
@@ -5736,7 +7013,7 @@
         <v>13</v>
       </c>
       <c r="I7" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="J7">
         <f>COUNT(G2:G21)</f>
@@ -5770,7 +7047,7 @@
         <v>19</v>
       </c>
       <c r="I8" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="J8">
         <f>COUNTA(D2:D21)</f>
@@ -5811,7 +7088,7 @@
         <v>15</v>
       </c>
       <c r="I9" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="J9">
         <f>COUNTBLANK(C2:C21)</f>
@@ -5852,7 +7129,7 @@
         <v>17</v>
       </c>
       <c r="I10" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="L10" t="s">
         <v>143</v>
@@ -5886,7 +7163,7 @@
         <v>11</v>
       </c>
       <c r="I11" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
@@ -5916,7 +7193,7 @@
         <v>5</v>
       </c>
       <c r="I12" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
@@ -5946,7 +7223,7 @@
         <v>8</v>
       </c>
       <c r="I13" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
@@ -5976,7 +7253,7 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
@@ -6006,7 +7283,7 @@
         <v>13</v>
       </c>
       <c r="I15" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="L15" t="s">
         <v>139</v>
@@ -6039,10 +7316,10 @@
         <v>19</v>
       </c>
       <c r="I16" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="L16" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
@@ -6069,7 +7346,7 @@
         <v>15</v>
       </c>
       <c r="I17" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="L17" t="s">
         <v>140</v>
@@ -6185,18 +7462,18 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="H24" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="J28" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="K28" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="L28" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.35">
@@ -6506,7 +7783,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="H13" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -6978,7 +8255,7 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.35">
       <c r="E16" s="1" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="R16">
         <v>10000</v>

--- a/Basic Practise File.xlsx
+++ b/Basic Practise File.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64130EE8-03A7-4F4C-9026-546503E5033B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA7CA01B-DADB-495A-974D-81796C51211E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="955" firstSheet="6" activeTab="11" xr2:uid="{804A284F-30AB-4AA4-80D9-3863464D9C5B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="955" firstSheet="6" activeTab="13" xr2:uid="{804A284F-30AB-4AA4-80D9-3863464D9C5B}"/>
   </bookViews>
   <sheets>
     <sheet name="Introduction" sheetId="13" r:id="rId1"/>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="441">
   <si>
     <t>Employee Name</t>
   </si>
@@ -1317,9 +1317,6 @@
     <t>if you want any text qualifers</t>
   </si>
   <si>
-    <t>then</t>
-  </si>
-  <si>
     <t>jp kumar</t>
   </si>
   <si>
@@ -1393,6 +1390,12 @@
   </si>
   <si>
     <t>click of</t>
+  </si>
+  <si>
+    <t>then select the destination where to display</t>
+  </si>
+  <si>
+    <t>then click finish</t>
   </si>
 </sst>
 </file>
@@ -2421,7 +2424,7 @@
       </c>
       <c r="C5" s="6">
         <f ca="1">NOW()</f>
-        <v>46157.946482754633</v>
+        <v>46157.949963310188</v>
       </c>
       <c r="D5" s="6"/>
     </row>
@@ -2434,7 +2437,7 @@
       </c>
       <c r="C6" s="7">
         <f ca="1">NOW()-TODAY()</f>
-        <v>0.94648275463259779</v>
+        <v>0.94996331018774072</v>
       </c>
       <c r="D6" t="s">
         <v>180</v>
@@ -2986,7 +2989,7 @@
         <v>364</v>
       </c>
       <c r="N16" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.35">
@@ -3003,7 +3006,7 @@
         <v>335</v>
       </c>
       <c r="N17" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.35">
@@ -3020,7 +3023,7 @@
         <v>322</v>
       </c>
       <c r="N18" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.35">
@@ -3030,7 +3033,7 @@
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.35">
       <c r="N20" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
   </sheetData>
@@ -3516,10 +3519,10 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BBACF5E-B802-4707-BE70-A8315AA524C2}">
   <sheetPr codeName="Sheet15"/>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.54296875" customWidth="1"/>
+    <col min="1" max="1" width="37.6328125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.36328125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.08984375" bestFit="1" customWidth="1"/>
   </cols>
@@ -3830,193 +3833,203 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>400</v>
-      </c>
-      <c r="B24" t="s">
-        <v>369</v>
-      </c>
-      <c r="C24">
-        <v>5</v>
-      </c>
-      <c r="D24" t="s">
-        <v>370</v>
-      </c>
-      <c r="E24">
-        <v>8562</v>
+        <v>439</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>401</v>
-      </c>
-      <c r="B25" t="s">
-        <v>371</v>
-      </c>
-      <c r="C25">
-        <v>5</v>
-      </c>
-      <c r="D25" t="s">
-        <v>372</v>
-      </c>
-      <c r="E25">
-        <v>9845</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>402</v>
-      </c>
-      <c r="B26" t="s">
-        <v>373</v>
-      </c>
-      <c r="C26">
-        <v>10</v>
-      </c>
-      <c r="D26" t="s">
-        <v>374</v>
-      </c>
-      <c r="E26">
-        <v>9878</v>
+        <v>440</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="B27" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C27">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D27" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="E27">
-        <v>2378</v>
+        <v>8562</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B28" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="C28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D28" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="E28">
-        <v>9567</v>
+        <v>9845</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="B29" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="C29">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D29" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="E29">
-        <v>8923</v>
+        <v>9878</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B30" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="C30">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D30" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="E30">
-        <v>5679</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B31" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="C31">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D31" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E31">
-        <v>7453</v>
+        <v>9567</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="B32" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="C32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D32" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="E32">
-        <v>4598</v>
+        <v>8923</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="B33" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="C33">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D33" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="E33">
-        <v>8345</v>
+        <v>5679</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
+        <v>407</v>
+      </c>
+      <c r="B34" t="s">
+        <v>382</v>
+      </c>
+      <c r="C34">
+        <v>9</v>
+      </c>
+      <c r="D34" t="s">
+        <v>379</v>
+      </c>
+      <c r="E34">
+        <v>7453</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>408</v>
+      </c>
+      <c r="B35" t="s">
+        <v>383</v>
+      </c>
+      <c r="C35">
+        <v>6</v>
+      </c>
+      <c r="D35" t="s">
+        <v>384</v>
+      </c>
+      <c r="E35">
+        <v>4598</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>409</v>
+      </c>
+      <c r="B36" t="s">
+        <v>385</v>
+      </c>
+      <c r="C36">
+        <v>3</v>
+      </c>
+      <c r="D36" t="s">
+        <v>386</v>
+      </c>
+      <c r="E36">
+        <v>8345</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
         <v>410</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B37" t="s">
         <v>387</v>
       </c>
-      <c r="C34">
+      <c r="C37">
         <v>5</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D37" t="s">
         <v>372</v>
       </c>
-      <c r="E34">
+      <c r="E37">
         <v>3456</v>
       </c>
     </row>
@@ -4067,13 +4080,13 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="F2" s="11"/>
     </row>
@@ -4085,10 +4098,10 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
@@ -4101,10 +4114,10 @@
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
@@ -4117,10 +4130,10 @@
         <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
@@ -4133,10 +4146,10 @@
         <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
@@ -4149,10 +4162,10 @@
         <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
@@ -4165,10 +4178,10 @@
         <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
@@ -4181,10 +4194,10 @@
         <v>37</v>
       </c>
       <c r="C9" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
@@ -4197,10 +4210,10 @@
         <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
@@ -4213,10 +4226,10 @@
         <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
@@ -5984,7 +5997,7 @@
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13">
         <f ca="1">RAND()</f>
-        <v>0.78148092061372865</v>
+        <v>0.29646970589883925</v>
       </c>
       <c r="I13" t="s">
         <v>290</v>
